--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D78BF0D-03B4-4C23-9CD8-D6E1CF94B9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4B7AA4-9FF5-432C-81E5-EBFA8D060322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1220FF07-3A76-449E-AAF6-6E1D51A9AEAB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{83CDC8D8-158E-488C-86E3-BE24D9525769}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_UZ_PER_loopback_tutoria" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Name</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>TSW-115-XX-YY-D</t>
+  </si>
+  <si>
+    <t>C5994596</t>
   </si>
   <si>
     <t/>
@@ -590,7 +593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE729ADC-36B1-4DA4-A45E-67B910508552}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB31AB-FAD7-4681-8AF8-D108315938B1}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -800,17 +803,19 @@
       <c r="C15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1"/>
     </row>

--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E4B7AA4-9FF5-432C-81E5-EBFA8D060322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F7092D-2EB6-497D-9060-5B15858626BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{83CDC8D8-158E-488C-86E3-BE24D9525769}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{063E0349-E7B7-45A8-B0E6-4B88E47FEC12}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_UZ_PER_loopback_tutoria" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -119,10 +119,10 @@
     <t>10k</t>
   </si>
   <si>
-    <t>LPF0_R2, LPF1_R2, LPF2_R2, LPF3_R2, LPF4_R2, LPF5_R2</t>
-  </si>
-  <si>
-    <t>C95204</t>
+    <t>LPF0_R2, LPF1_R2, LPF2_R2, LPF3_R2, LPF4_R2, LPF5_R2, R3, R5, R7, R9, R11, R13</t>
+  </si>
+  <si>
+    <t>C95204, C25804</t>
   </si>
   <si>
     <t>24k9</t>
@@ -132,15 +132,6 @@
   </si>
   <si>
     <t>C844763</t>
-  </si>
-  <si>
-    <t>2k2</t>
-  </si>
-  <si>
-    <t>R3, R5, R7, R9, R11, R13</t>
-  </si>
-  <si>
-    <t>C4190</t>
   </si>
   <si>
     <t>4k3</t>
@@ -593,8 +584,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB31AB-FAD7-4681-8AF8-D108315938B1}">
-  <dimension ref="A1:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA54D5-4319-4F6E-A614-5ED6DC83E13A}">
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" customWidth="1"/>
@@ -739,19 +730,17 @@
       <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -765,21 +754,21 @@
       <c r="C12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -791,33 +780,21 @@
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="1"/>
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
+++ b/Project Outputs for UZ_PER_loopback_tutorial/Rev02/BOM_JLC/BOM_JLC_UZ_PER_loopback_tutorial_[No Variations]_Rev02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johan\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F7092D-2EB6-497D-9060-5B15858626BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3666E93B-84A0-405D-9F9A-244931BBA24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{063E0349-E7B7-45A8-B0E6-4B88E47FEC12}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0CDB69C1-70EF-4D02-B273-8D5B123C8D5B}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_UZ_PER_loopback_tutoria" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -53,7 +53,7 @@
     <t>LCSC Part #</t>
   </si>
   <si>
-    <t>150060BS84000</t>
+    <t>LED Blue</t>
   </si>
   <si>
     <t>D0, D1, D4</t>
@@ -65,22 +65,22 @@
     <t>C5197644</t>
   </si>
   <si>
-    <t>150060GS84000</t>
+    <t>LED Green</t>
   </si>
   <si>
     <t>D2, D5</t>
   </si>
   <si>
-    <t>C72043</t>
-  </si>
-  <si>
-    <t>150060RS86000</t>
+    <t>C5252984</t>
+  </si>
+  <si>
+    <t>LED Red</t>
   </si>
   <si>
     <t>D3, D6</t>
   </si>
   <si>
-    <t>C389517</t>
+    <t>C3030991</t>
   </si>
   <si>
     <t>1 µF</t>
@@ -92,7 +92,7 @@
     <t>C_0603</t>
   </si>
   <si>
-    <t>C105174</t>
+    <t>C15849</t>
   </si>
   <si>
     <t>100 nF</t>
@@ -101,7 +101,7 @@
     <t>LPF0_C2, LPF1_C2, LPF2_C2, LPF3_C2, LPF4_C2, LPF5_C2</t>
   </si>
   <si>
-    <t>C696358</t>
+    <t>C14663</t>
   </si>
   <si>
     <t>1k</t>
@@ -119,27 +119,21 @@
     <t>10k</t>
   </si>
   <si>
-    <t>LPF0_R2, LPF1_R2, LPF2_R2, LPF3_R2, LPF4_R2, LPF5_R2, R3, R5, R7, R9, R11, R13</t>
-  </si>
-  <si>
-    <t>C95204, C25804</t>
-  </si>
-  <si>
-    <t>24k9</t>
-  </si>
-  <si>
-    <t>R0</t>
-  </si>
-  <si>
-    <t>C844763</t>
-  </si>
-  <si>
-    <t>4k3</t>
+    <t>LPF0_R2, LPF1_R2, LPF2_R2, LPF3_R2, LPF4_R2, LPF5_R2, R0, R0b, R3, R3b, R5, R5b, R7, R7b, R9, R9b, R11, R11b, R13, R13b</t>
+  </si>
+  <si>
+    <t>C25804</t>
+  </si>
+  <si>
+    <t>43k</t>
   </si>
   <si>
     <t>R4, R6, R8, R10, R12, R14</t>
   </si>
   <si>
+    <t>C23172</t>
+  </si>
+  <si>
     <t>Serial #</t>
   </si>
   <si>
@@ -170,6 +164,9 @@
     <t>IPL1-115-01-YYY-D-K</t>
   </si>
   <si>
+    <t>C17431809</t>
+  </si>
+  <si>
     <t>TSW-115-07-G-D</t>
   </si>
   <si>
@@ -189,6 +186,9 @@
   </si>
   <si>
     <t>RJHSE-5380-02</t>
+  </si>
+  <si>
+    <t>C47326523</t>
   </si>
 </sst>
 </file>
@@ -584,8 +584,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA54D5-4319-4F6E-A614-5ED6DC83E13A}">
-  <dimension ref="A1:D15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E1E097-DC20-4EEE-B606-3791775CBA22}">
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" customWidth="1"/>
@@ -728,73 +728,65 @@
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
